--- a/data/nzd0083/nzd0083.xlsx
+++ b/data/nzd0083/nzd0083.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G339"/>
+  <dimension ref="A1:G340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9591,6 +9591,33 @@
       <c r="G339" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>336.19</v>
+      </c>
+      <c r="C340" t="n">
+        <v>329.15</v>
+      </c>
+      <c r="D340" t="n">
+        <v>337.11</v>
+      </c>
+      <c r="E340" t="n">
+        <v>338.2</v>
+      </c>
+      <c r="F340" t="n">
+        <v>346.13</v>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -9605,7 +9632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B351"/>
+  <dimension ref="A1:B352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13118,6 +13145,16 @@
       </c>
       <c r="B351" t="n">
         <v>-0.38</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>
@@ -13286,28 +13323,28 @@
         <v>0.1314</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2764756073651981</v>
+        <v>0.2756871433967046</v>
       </c>
       <c r="J2" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K2" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1048974600146363</v>
+        <v>0.1049799173090419</v>
       </c>
       <c r="M2" t="n">
-        <v>4.539077164118537</v>
+        <v>4.529177381653949</v>
       </c>
       <c r="N2" t="n">
-        <v>33.45058376354996</v>
+        <v>33.35664747160987</v>
       </c>
       <c r="O2" t="n">
-        <v>5.783647963314327</v>
+        <v>5.77552140257569</v>
       </c>
       <c r="P2" t="n">
-        <v>330.2260169005713</v>
+        <v>330.2343957168987</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13364,28 +13401,28 @@
         <v>0.1036</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1924982076212878</v>
+        <v>0.1916719237683846</v>
       </c>
       <c r="J3" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K3" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05180316953067532</v>
+        <v>0.05170396020771162</v>
       </c>
       <c r="M3" t="n">
-        <v>4.745889044229461</v>
+        <v>4.735462124192383</v>
       </c>
       <c r="N3" t="n">
-        <v>34.78386120262954</v>
+        <v>34.68645737056364</v>
       </c>
       <c r="O3" t="n">
-        <v>5.897784431685303</v>
+        <v>5.889520979720137</v>
       </c>
       <c r="P3" t="n">
-        <v>325.446954001603</v>
+        <v>325.4557347207157</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13442,28 +13479,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09444875589423819</v>
+        <v>0.09100052104355535</v>
       </c>
       <c r="J4" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K4" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02461482064473153</v>
+        <v>0.02292943431396688</v>
       </c>
       <c r="M4" t="n">
-        <v>3.531802356492266</v>
+        <v>3.535672796192713</v>
       </c>
       <c r="N4" t="n">
-        <v>18.12817990433292</v>
+        <v>18.16532458167274</v>
       </c>
       <c r="O4" t="n">
-        <v>4.257720035926848</v>
+        <v>4.262079842245185</v>
       </c>
       <c r="P4" t="n">
-        <v>340.2003341132599</v>
+        <v>340.2369776729183</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13520,28 +13557,28 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.08403530022275331</v>
+        <v>0.07806120731281933</v>
       </c>
       <c r="J5" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K5" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01088322232851957</v>
+        <v>0.00939070540587672</v>
       </c>
       <c r="M5" t="n">
-        <v>4.545560764316149</v>
+        <v>4.553248834719883</v>
       </c>
       <c r="N5" t="n">
-        <v>32.91514871924899</v>
+        <v>33.09005768612554</v>
       </c>
       <c r="O5" t="n">
-        <v>5.737172536994943</v>
+        <v>5.752395821405681</v>
       </c>
       <c r="P5" t="n">
-        <v>345.6478164492752</v>
+        <v>345.7113016930099</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -13598,28 +13635,28 @@
         <v>0.1022</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2738468893753028</v>
+        <v>0.2681468113808666</v>
       </c>
       <c r="J6" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K6" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07522966116084784</v>
+        <v>0.0724549303835631</v>
       </c>
       <c r="M6" t="n">
-        <v>5.445707647099107</v>
+        <v>5.454243818213371</v>
       </c>
       <c r="N6" t="n">
-        <v>47.27620996080647</v>
+        <v>47.3843760512053</v>
       </c>
       <c r="O6" t="n">
-        <v>6.875769772236885</v>
+        <v>6.883631022302495</v>
       </c>
       <c r="P6" t="n">
-        <v>348.1658343675938</v>
+        <v>348.2264077209445</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -13657,7 +13694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G339"/>
+  <dimension ref="A1:G340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26203,6 +26240,43 @@
         </is>
       </c>
     </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>-35.503275702428084,174.46927956477515</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>-35.503987533512216,174.46950294131557</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>-35.50466072638454,174.46988518881432</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>-35.50534967583807,174.4702591990294</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>-35.50594014482626,174.47079571759548</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0083/nzd0083.xlsx
+++ b/data/nzd0083/nzd0083.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G340"/>
+  <dimension ref="A1:G341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9616,6 +9616,33 @@
         <v>346.13</v>
       </c>
       <c r="G340" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>335.49</v>
+      </c>
+      <c r="C341" t="n">
+        <v>329.53</v>
+      </c>
+      <c r="D341" t="n">
+        <v>337.35</v>
+      </c>
+      <c r="E341" t="n">
+        <v>339.92</v>
+      </c>
+      <c r="F341" t="n">
+        <v>346.52</v>
+      </c>
+      <c r="G341" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -9632,7 +9659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B352"/>
+  <dimension ref="A1:B353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13155,6 +13182,16 @@
       </c>
       <c r="B352" t="n">
         <v>1.13</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>0.71</v>
       </c>
     </row>
   </sheetData>
@@ -13323,28 +13360,28 @@
         <v>0.1314</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2756871433967046</v>
+        <v>0.2744559571004732</v>
       </c>
       <c r="J2" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K2" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1049799173090419</v>
+        <v>0.1047411503327959</v>
       </c>
       <c r="M2" t="n">
-        <v>4.529177381653949</v>
+        <v>4.521241589876055</v>
       </c>
       <c r="N2" t="n">
-        <v>33.35664747160987</v>
+        <v>33.27009559590186</v>
       </c>
       <c r="O2" t="n">
-        <v>5.77552140257569</v>
+        <v>5.768023543286024</v>
       </c>
       <c r="P2" t="n">
-        <v>330.2343957168987</v>
+        <v>330.2475264201837</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13401,28 +13438,28 @@
         <v>0.1036</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1916719237683846</v>
+        <v>0.1910789989471083</v>
       </c>
       <c r="J3" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K3" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05170396020771162</v>
+        <v>0.05172757246482851</v>
       </c>
       <c r="M3" t="n">
-        <v>4.735462124192383</v>
+        <v>4.724066163047802</v>
       </c>
       <c r="N3" t="n">
-        <v>34.68645737056364</v>
+        <v>34.58711850857005</v>
       </c>
       <c r="O3" t="n">
-        <v>5.889520979720137</v>
+        <v>5.881081406388629</v>
       </c>
       <c r="P3" t="n">
-        <v>325.4557347207157</v>
+        <v>325.4620583127848</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13479,28 +13516,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09100052104355535</v>
+        <v>0.08773846420524044</v>
       </c>
       <c r="J4" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K4" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02292943431396688</v>
+        <v>0.02139730727096489</v>
       </c>
       <c r="M4" t="n">
-        <v>3.535672796192713</v>
+        <v>3.538960231121041</v>
       </c>
       <c r="N4" t="n">
-        <v>18.16532458167274</v>
+        <v>18.1930193507178</v>
       </c>
       <c r="O4" t="n">
-        <v>4.262079842245185</v>
+        <v>4.265327578359932</v>
       </c>
       <c r="P4" t="n">
-        <v>340.2369776729183</v>
+        <v>340.2717677778552</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13557,28 +13594,28 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07806120731281933</v>
+        <v>0.07321531218623475</v>
       </c>
       <c r="J5" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K5" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00939070540587672</v>
+        <v>0.008281353159761529</v>
       </c>
       <c r="M5" t="n">
-        <v>4.553248834719883</v>
+        <v>4.556836408355659</v>
       </c>
       <c r="N5" t="n">
-        <v>33.09005768612554</v>
+        <v>33.17175526935756</v>
       </c>
       <c r="O5" t="n">
-        <v>5.752395821405681</v>
+        <v>5.759492622562995</v>
       </c>
       <c r="P5" t="n">
-        <v>345.7113016930099</v>
+        <v>345.7629835637814</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -13635,28 +13672,28 @@
         <v>0.1022</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2681468113808666</v>
+        <v>0.2627335633115031</v>
       </c>
       <c r="J6" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K6" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0724549303835631</v>
+        <v>0.06989347121789924</v>
       </c>
       <c r="M6" t="n">
-        <v>5.454243818213371</v>
+        <v>5.461286850414796</v>
       </c>
       <c r="N6" t="n">
-        <v>47.3843760512053</v>
+        <v>47.46840475182238</v>
       </c>
       <c r="O6" t="n">
-        <v>6.883631022302495</v>
+        <v>6.88973183453626</v>
       </c>
       <c r="P6" t="n">
-        <v>348.2264077209445</v>
+        <v>348.2841404575942</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -13694,7 +13731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G340"/>
+  <dimension ref="A1:G341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26277,6 +26314,43 @@
         </is>
       </c>
     </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>-35.50327783896804,174.46927230359424</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>-35.5039863736717,174.46950688313183</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>-35.50465992700877,174.46988764745305</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>-35.505342520125936,174.47027602111442</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>-35.505938309549414,174.470799384865</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0083/nzd0083.xlsx
+++ b/data/nzd0083/nzd0083.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G341"/>
+  <dimension ref="A1:G342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9645,6 +9645,33 @@
       <c r="G341" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:44+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>337.33</v>
+      </c>
+      <c r="C342" t="n">
+        <v>327.37</v>
+      </c>
+      <c r="D342" t="n">
+        <v>341.78</v>
+      </c>
+      <c r="E342" t="n">
+        <v>346.65</v>
+      </c>
+      <c r="F342" t="n">
+        <v>351.17</v>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -9659,7 +9686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B353"/>
+  <dimension ref="A1:B354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13192,6 +13219,16 @@
       </c>
       <c r="B353" t="n">
         <v>0.71</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>
@@ -13360,28 +13397,28 @@
         <v>0.1314</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2744559571004732</v>
+        <v>0.2743484247132608</v>
       </c>
       <c r="J2" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K2" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1047411503327959</v>
+        <v>0.1053120364678749</v>
       </c>
       <c r="M2" t="n">
-        <v>4.521241589876055</v>
+        <v>4.508444566322288</v>
       </c>
       <c r="N2" t="n">
-        <v>33.27009559590186</v>
+        <v>33.17261647981341</v>
       </c>
       <c r="O2" t="n">
-        <v>5.768023543286024</v>
+        <v>5.759567386515537</v>
       </c>
       <c r="P2" t="n">
-        <v>330.2475264201837</v>
+        <v>330.2486803849382</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13438,28 +13475,28 @@
         <v>0.1036</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1910789989471083</v>
+        <v>0.1891301536989335</v>
       </c>
       <c r="J3" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K3" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05172757246482851</v>
+        <v>0.05102224261465194</v>
       </c>
       <c r="M3" t="n">
-        <v>4.724066163047802</v>
+        <v>4.718372224047497</v>
       </c>
       <c r="N3" t="n">
-        <v>34.58711850857005</v>
+        <v>34.51431378042341</v>
       </c>
       <c r="O3" t="n">
-        <v>5.881081406388629</v>
+        <v>5.874888405784693</v>
       </c>
       <c r="P3" t="n">
-        <v>325.4620583127848</v>
+        <v>325.4829720001533</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13516,28 +13553,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08773846420524044</v>
+        <v>0.08723176564402829</v>
       </c>
       <c r="J4" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K4" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02139730727096489</v>
+        <v>0.02129639403185979</v>
       </c>
       <c r="M4" t="n">
-        <v>3.538960231121041</v>
+        <v>3.530691357739062</v>
       </c>
       <c r="N4" t="n">
-        <v>18.1930193507178</v>
+        <v>18.14160234560119</v>
       </c>
       <c r="O4" t="n">
-        <v>4.265327578359932</v>
+        <v>4.259295991780941</v>
       </c>
       <c r="P4" t="n">
-        <v>340.2717677778552</v>
+        <v>340.2772053236578</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13594,28 +13631,28 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07321531218623475</v>
+        <v>0.07256650249803334</v>
       </c>
       <c r="J5" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K5" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L5" t="n">
-        <v>0.008281353159761529</v>
+        <v>0.008191188151262518</v>
       </c>
       <c r="M5" t="n">
-        <v>4.556836408355659</v>
+        <v>4.545700620146492</v>
       </c>
       <c r="N5" t="n">
-        <v>33.17175526935756</v>
+        <v>33.07764993246934</v>
       </c>
       <c r="O5" t="n">
-        <v>5.759492622562995</v>
+        <v>5.751317234553259</v>
       </c>
       <c r="P5" t="n">
-        <v>345.7629835637814</v>
+        <v>345.7699461499556</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -13672,28 +13709,28 @@
         <v>0.1022</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2627335633115031</v>
+        <v>0.2602133947223035</v>
       </c>
       <c r="J6" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K6" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06989347121789924</v>
+        <v>0.06902558083049359</v>
       </c>
       <c r="M6" t="n">
-        <v>5.461286850414796</v>
+        <v>5.455819722122027</v>
       </c>
       <c r="N6" t="n">
-        <v>47.46840475182238</v>
+        <v>47.37706768231013</v>
       </c>
       <c r="O6" t="n">
-        <v>6.88973183453626</v>
+        <v>6.883100150536103</v>
       </c>
       <c r="P6" t="n">
-        <v>348.2841404575942</v>
+        <v>348.3111852001358</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -13731,7 +13768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G341"/>
+  <dimension ref="A1:G342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26351,6 +26388,43 @@
         </is>
       </c>
     </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:44+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>-35.50327222291922,174.46929139012605</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>-35.503992966447704,174.46948447701672</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>-35.5046451718555,174.4699330298177</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>-35.50531452130016,174.47034184238285</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>-35.505916427394,174.47084310998864</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0083/nzd0083.xlsx
+++ b/data/nzd0083/nzd0083.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G342"/>
+  <dimension ref="A1:G343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9670,6 +9670,33 @@
         <v>351.17</v>
       </c>
       <c r="G342" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>337.57</v>
+      </c>
+      <c r="C343" t="n">
+        <v>326.99</v>
+      </c>
+      <c r="D343" t="n">
+        <v>341.24</v>
+      </c>
+      <c r="E343" t="n">
+        <v>346.24</v>
+      </c>
+      <c r="F343" t="n">
+        <v>351.11</v>
+      </c>
+      <c r="G343" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -9686,7 +9713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B354"/>
+  <dimension ref="A1:B355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13229,6 +13256,16 @@
       </c>
       <c r="B354" t="n">
         <v>0.88</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>0.97</v>
       </c>
     </row>
   </sheetData>
@@ -13397,28 +13434,28 @@
         <v>0.1314</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2743484247132608</v>
+        <v>0.2743832563732392</v>
       </c>
       <c r="J2" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K2" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1053120364678749</v>
+        <v>0.1059810908954443</v>
       </c>
       <c r="M2" t="n">
-        <v>4.508444566322288</v>
+        <v>4.495440353134633</v>
       </c>
       <c r="N2" t="n">
-        <v>33.17261647981341</v>
+        <v>33.07562974840675</v>
       </c>
       <c r="O2" t="n">
-        <v>5.759567386515537</v>
+        <v>5.751141603925846</v>
       </c>
       <c r="P2" t="n">
-        <v>330.2486803849382</v>
+        <v>330.2483059413207</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13475,28 +13512,28 @@
         <v>0.1036</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1891301536989335</v>
+        <v>0.1869713717898099</v>
       </c>
       <c r="J3" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K3" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05102224261465194</v>
+        <v>0.05019768113036593</v>
       </c>
       <c r="M3" t="n">
-        <v>4.718372224047497</v>
+        <v>4.713595308742473</v>
       </c>
       <c r="N3" t="n">
-        <v>34.51431378042341</v>
+        <v>34.4488231244356</v>
       </c>
       <c r="O3" t="n">
-        <v>5.874888405784693</v>
+        <v>5.869311980499554</v>
       </c>
       <c r="P3" t="n">
-        <v>325.4829720001533</v>
+        <v>325.5061791085109</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13553,28 +13590,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08723176564402829</v>
+        <v>0.08640282270423566</v>
       </c>
       <c r="J4" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K4" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02129639403185979</v>
+        <v>0.02103622260818161</v>
       </c>
       <c r="M4" t="n">
-        <v>3.530691357739062</v>
+        <v>3.523793722045971</v>
       </c>
       <c r="N4" t="n">
-        <v>18.14160234560119</v>
+        <v>18.09378048395154</v>
       </c>
       <c r="O4" t="n">
-        <v>4.259295991780941</v>
+        <v>4.253678465040763</v>
       </c>
       <c r="P4" t="n">
-        <v>340.2772053236578</v>
+        <v>340.2861165381464</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13631,28 +13668,28 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07256650249803334</v>
+        <v>0.07167220332550231</v>
       </c>
       <c r="J5" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K5" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L5" t="n">
-        <v>0.008191188151262518</v>
+        <v>0.008044982566422609</v>
       </c>
       <c r="M5" t="n">
-        <v>4.545700620146492</v>
+        <v>4.535454941956067</v>
       </c>
       <c r="N5" t="n">
-        <v>33.07764993246934</v>
+        <v>32.98701160121674</v>
       </c>
       <c r="O5" t="n">
-        <v>5.751317234553259</v>
+        <v>5.743432040271457</v>
       </c>
       <c r="P5" t="n">
-        <v>345.7699461499556</v>
+        <v>345.7795599500869</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -13709,28 +13746,28 @@
         <v>0.1022</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2602133947223035</v>
+        <v>0.2576865564705589</v>
       </c>
       <c r="J6" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K6" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06902558083049359</v>
+        <v>0.06814938505311674</v>
       </c>
       <c r="M6" t="n">
-        <v>5.455819722122027</v>
+        <v>5.450364968361569</v>
       </c>
       <c r="N6" t="n">
-        <v>47.37706768231013</v>
+        <v>47.28707701434017</v>
       </c>
       <c r="O6" t="n">
-        <v>6.883100150536103</v>
+        <v>6.876559969515293</v>
       </c>
       <c r="P6" t="n">
-        <v>348.3111852001358</v>
+        <v>348.3383489487584</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -13768,7 +13805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G342"/>
+  <dimension ref="A1:G343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26425,6 +26462,43 @@
         </is>
       </c>
     </row>
+    <row r="343">
+      <c r="A343" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>-35.5032714903909,174.46929387967347</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>-35.50399412628751,174.46948053519978</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>-35.50464697045296,174.46992749788254</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>-35.505316227024565,174.47033783247034</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>-35.5059167097445,174.47084254579366</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0083/nzd0083.xlsx
+++ b/data/nzd0083/nzd0083.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G343"/>
+  <dimension ref="A1:G345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9699,6 +9699,60 @@
       <c r="G343" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>335.16</v>
+      </c>
+      <c r="C344" t="n">
+        <v>324.25</v>
+      </c>
+      <c r="D344" t="n">
+        <v>338.8</v>
+      </c>
+      <c r="E344" t="n">
+        <v>344.28</v>
+      </c>
+      <c r="F344" t="n">
+        <v>347.72</v>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>334.1</v>
+      </c>
+      <c r="C345" t="n">
+        <v>324.19</v>
+      </c>
+      <c r="D345" t="n">
+        <v>338.82</v>
+      </c>
+      <c r="E345" t="n">
+        <v>342.37</v>
+      </c>
+      <c r="F345" t="n">
+        <v>345.19</v>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -9713,7 +9767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B355"/>
+  <dimension ref="A1:B357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13266,6 +13320,26 @@
       </c>
       <c r="B355" t="n">
         <v>0.97</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>-0.1</v>
       </c>
     </row>
   </sheetData>
@@ -13434,28 +13508,28 @@
         <v>0.1314</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2743832563732392</v>
+        <v>0.2707955100004504</v>
       </c>
       <c r="J2" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K2" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1059810908954443</v>
+        <v>0.1046515660060138</v>
       </c>
       <c r="M2" t="n">
-        <v>4.495440353134633</v>
+        <v>4.484666565395905</v>
       </c>
       <c r="N2" t="n">
-        <v>33.07562974840675</v>
+        <v>32.93377599835042</v>
       </c>
       <c r="O2" t="n">
-        <v>5.751141603925846</v>
+        <v>5.738795692333926</v>
       </c>
       <c r="P2" t="n">
-        <v>330.2483059413207</v>
+        <v>330.2870949408265</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13512,28 +13586,28 @@
         <v>0.1036</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1869713717898099</v>
+        <v>0.1792913165779248</v>
       </c>
       <c r="J3" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K3" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05019768113036593</v>
+        <v>0.04666658958765213</v>
       </c>
       <c r="M3" t="n">
-        <v>4.713595308742473</v>
+        <v>4.717682430087858</v>
       </c>
       <c r="N3" t="n">
-        <v>34.4488231244356</v>
+        <v>34.47224159368731</v>
       </c>
       <c r="O3" t="n">
-        <v>5.869311980499554</v>
+        <v>5.871306634275483</v>
       </c>
       <c r="P3" t="n">
-        <v>325.5061791085109</v>
+        <v>325.5892058376811</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13590,28 +13664,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08640282270423566</v>
+        <v>0.0817677634822382</v>
       </c>
       <c r="J4" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K4" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02103622260818161</v>
+        <v>0.01905295666612195</v>
       </c>
       <c r="M4" t="n">
-        <v>3.523793722045971</v>
+        <v>3.522089120119284</v>
       </c>
       <c r="N4" t="n">
-        <v>18.09378048395154</v>
+        <v>18.07006368298007</v>
       </c>
       <c r="O4" t="n">
-        <v>4.253678465040763</v>
+        <v>4.250889751920187</v>
       </c>
       <c r="P4" t="n">
-        <v>340.2861165381464</v>
+        <v>340.3362245773981</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13668,28 +13742,28 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07167220332550231</v>
+        <v>0.06632451785092877</v>
       </c>
       <c r="J5" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K5" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L5" t="n">
-        <v>0.008044982566422609</v>
+        <v>0.006968029386979824</v>
       </c>
       <c r="M5" t="n">
-        <v>4.535454941956067</v>
+        <v>4.526894733912294</v>
       </c>
       <c r="N5" t="n">
-        <v>32.98701160121674</v>
+        <v>32.90892701368316</v>
       </c>
       <c r="O5" t="n">
-        <v>5.743432040271457</v>
+        <v>5.736630283858561</v>
       </c>
       <c r="P5" t="n">
-        <v>345.7795599500869</v>
+        <v>345.8373774937074</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -13746,28 +13820,28 @@
         <v>0.1022</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2576865564705589</v>
+        <v>0.2469673241181839</v>
       </c>
       <c r="J6" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K6" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06814938505311674</v>
+        <v>0.06320264797768038</v>
       </c>
       <c r="M6" t="n">
-        <v>5.450364968361569</v>
+        <v>5.462298927550376</v>
       </c>
       <c r="N6" t="n">
-        <v>47.28707701434017</v>
+        <v>47.45714797304728</v>
       </c>
       <c r="O6" t="n">
-        <v>6.876559969515293</v>
+        <v>6.888914861794075</v>
       </c>
       <c r="P6" t="n">
-        <v>348.3383489487584</v>
+        <v>348.4542383156473</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -13805,7 +13879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G343"/>
+  <dimension ref="A1:G345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26499,6 +26573,80 @@
         </is>
       </c>
     </row>
+    <row r="344">
+      <c r="A344" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>-35.503278846193865,174.46926888046596</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>-35.504002489339186,174.4694521126215</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>-35.50465509744577,174.4699025017278</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>-35.505324381217534,174.47031866313017</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>-35.505932662543024,174.47081066877018</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>-35.50328208152468,174.4692578849624</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>-35.50400267247163,174.4694514902292</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>-35.5046550308311,174.46990270661433</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>-35.505332327392516,174.4702999828</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>-35.5059445683136,174.47078687853488</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0083/nzd0083.xlsx
+++ b/data/nzd0083/nzd0083.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G345"/>
+  <dimension ref="A1:G347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9753,6 +9753,60 @@
       <c r="G345" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>331.05</v>
+      </c>
+      <c r="C346" t="n">
+        <v>320.99</v>
+      </c>
+      <c r="D346" t="n">
+        <v>334.16</v>
+      </c>
+      <c r="E346" t="n">
+        <v>338.36</v>
+      </c>
+      <c r="F346" t="n">
+        <v>341.07</v>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>329.78</v>
+      </c>
+      <c r="C347" t="n">
+        <v>319.41</v>
+      </c>
+      <c r="D347" t="n">
+        <v>333.42</v>
+      </c>
+      <c r="E347" t="n">
+        <v>338.86</v>
+      </c>
+      <c r="F347" t="n">
+        <v>341.81</v>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -9767,7 +9821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B357"/>
+  <dimension ref="A1:B359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13340,6 +13394,26 @@
       </c>
       <c r="B357" t="n">
         <v>-0.1</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -13508,28 +13582,28 @@
         <v>0.1314</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2707955100004504</v>
+        <v>0.2622050203943915</v>
       </c>
       <c r="J2" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="K2" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1046515660060138</v>
+        <v>0.09919046596536385</v>
       </c>
       <c r="M2" t="n">
-        <v>4.484666565395905</v>
+        <v>4.495560642966616</v>
       </c>
       <c r="N2" t="n">
-        <v>32.93377599835042</v>
+        <v>33.03162390600433</v>
       </c>
       <c r="O2" t="n">
-        <v>5.738795692333926</v>
+        <v>5.747314495136344</v>
       </c>
       <c r="P2" t="n">
-        <v>330.2870949408265</v>
+        <v>330.3802078973151</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13586,28 +13660,28 @@
         <v>0.1036</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1792913165779248</v>
+        <v>0.1669816646654921</v>
       </c>
       <c r="J3" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="K3" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04666658958765213</v>
+        <v>0.04059319006554951</v>
       </c>
       <c r="M3" t="n">
-        <v>4.717682430087858</v>
+        <v>4.740765649184968</v>
       </c>
       <c r="N3" t="n">
-        <v>34.47224159368731</v>
+        <v>34.86358658437374</v>
       </c>
       <c r="O3" t="n">
-        <v>5.871306634275483</v>
+        <v>5.904539489610832</v>
       </c>
       <c r="P3" t="n">
-        <v>325.5892058376811</v>
+        <v>325.7226303731815</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13664,28 +13738,28 @@
         <v>0.07969999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0817677634822382</v>
+        <v>0.07120437726635512</v>
       </c>
       <c r="J4" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="K4" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01905295666612195</v>
+        <v>0.01436898228376593</v>
       </c>
       <c r="M4" t="n">
-        <v>3.522089120119284</v>
+        <v>3.544856415291918</v>
       </c>
       <c r="N4" t="n">
-        <v>18.07006368298007</v>
+        <v>18.39867779579505</v>
       </c>
       <c r="O4" t="n">
-        <v>4.250889751920187</v>
+        <v>4.289367994914292</v>
       </c>
       <c r="P4" t="n">
-        <v>340.3362245773981</v>
+        <v>340.4507195323874</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13742,28 +13816,28 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06632451785092877</v>
+        <v>0.05543848316088987</v>
       </c>
       <c r="J5" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="K5" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006968029386979824</v>
+        <v>0.004876762323718031</v>
       </c>
       <c r="M5" t="n">
-        <v>4.526894733912294</v>
+        <v>4.536899984084334</v>
       </c>
       <c r="N5" t="n">
-        <v>32.90892701368316</v>
+        <v>33.17820084672856</v>
       </c>
       <c r="O5" t="n">
-        <v>5.736630283858561</v>
+        <v>5.760052156597939</v>
       </c>
       <c r="P5" t="n">
-        <v>345.8373774937074</v>
+        <v>345.9553659858848</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -13820,28 +13894,28 @@
         <v>0.1022</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2469673241181839</v>
+        <v>0.2305041295810548</v>
       </c>
       <c r="J6" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="K6" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06320264797768038</v>
+        <v>0.05506713381686701</v>
       </c>
       <c r="M6" t="n">
-        <v>5.462298927550376</v>
+        <v>5.497503031244035</v>
       </c>
       <c r="N6" t="n">
-        <v>47.45714797304728</v>
+        <v>48.23372231224675</v>
       </c>
       <c r="O6" t="n">
-        <v>6.888914861794075</v>
+        <v>6.945050202284124</v>
       </c>
       <c r="P6" t="n">
-        <v>348.4542383156473</v>
+        <v>348.6326750056886</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -13879,7 +13953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G345"/>
+  <dimension ref="A1:G347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26647,6 +26721,80 @@
         </is>
       </c>
     </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-01 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>-35.5032913907258,174.4692262469518</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>-35.50401243953078,174.46941829596932</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>-35.50467055204106,174.46985496804217</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>-35.50534901019053,174.47026076387465</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>-35.50596395635714,174.4707481371088</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>-35.50329526701371,174.46921307308938</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>-35.504017262012944,174.46940190630042</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>-35.504673016780856,174.4698473872371</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>-35.50534693004182,174.47026565401586</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>-35.50596047403953,174.47075509552167</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
